--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/47.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/47.xlsx
@@ -426,13 +426,13 @@
         <v>-11.49462264887761</v>
       </c>
       <c r="E2">
-        <v>-7.549588648433138</v>
+        <v>-7.055523077248288</v>
       </c>
       <c r="F2">
-        <v>-2.562016268995959</v>
+        <v>-2.312075457651472</v>
       </c>
       <c r="G2">
-        <v>-7.695771453805539</v>
+        <v>-7.377720722756677</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.69022459578752</v>
       </c>
       <c r="E3">
-        <v>-7.88748526498947</v>
+        <v>-8.318102386852852</v>
       </c>
       <c r="F3">
-        <v>-2.459767566998805</v>
+        <v>-2.449355817113017</v>
       </c>
       <c r="G3">
-        <v>-6.788096009484782</v>
+        <v>-6.722550518352752</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.819249852199928</v>
       </c>
       <c r="E4">
-        <v>-8.331538369233609</v>
+        <v>-8.995639082458467</v>
       </c>
       <c r="F4">
-        <v>-2.656592632108384</v>
+        <v>-2.688194848525185</v>
       </c>
       <c r="G4">
-        <v>-6.856928872337309</v>
+        <v>-6.548601213537287</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.989326221410195</v>
       </c>
       <c r="E5">
-        <v>-9.433352323091869</v>
+        <v>-9.116042149374408</v>
       </c>
       <c r="F5">
-        <v>-2.446513688554012</v>
+        <v>-2.429879242738396</v>
       </c>
       <c r="G5">
-        <v>-6.423131537598909</v>
+        <v>-6.715366634532534</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.196468621521118</v>
       </c>
       <c r="E6">
-        <v>-9.679153363754208</v>
+        <v>-10.55471117076723</v>
       </c>
       <c r="F6">
-        <v>-2.860863063434325</v>
+        <v>-2.838317387832331</v>
       </c>
       <c r="G6">
-        <v>-5.916578343543946</v>
+        <v>-6.177740660045972</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.473449615068358</v>
       </c>
       <c r="E7">
-        <v>-9.743362596708966</v>
+        <v>-11.28837830169792</v>
       </c>
       <c r="F7">
-        <v>-2.88260108081859</v>
+        <v>-2.690872131971033</v>
       </c>
       <c r="G7">
-        <v>-5.564180702525146</v>
+        <v>-6.032553374875694</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.829164150453694</v>
       </c>
       <c r="E8">
-        <v>-11.25176558934591</v>
+        <v>-12.0031481105946</v>
       </c>
       <c r="F8">
-        <v>-2.826147013950401</v>
+        <v>-2.443714635099953</v>
       </c>
       <c r="G8">
-        <v>-4.644113886250897</v>
+        <v>-5.476795542470543</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.278232311112712</v>
       </c>
       <c r="E9">
-        <v>-12.58038816387834</v>
+        <v>-12.72210675794838</v>
       </c>
       <c r="F9">
-        <v>-2.578632490728714</v>
+        <v>-2.533444220538598</v>
       </c>
       <c r="G9">
-        <v>-5.096000041815875</v>
+        <v>-4.980902305052034</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.823434058185158</v>
       </c>
       <c r="E10">
-        <v>-13.19789087956427</v>
+        <v>-13.99802695197954</v>
       </c>
       <c r="F10">
-        <v>-2.967987535964357</v>
+        <v>-2.434663892856966</v>
       </c>
       <c r="G10">
-        <v>-4.632013842304861</v>
+        <v>-4.519475157242876</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.458803288895207</v>
       </c>
       <c r="E11">
-        <v>-13.27587573045036</v>
+        <v>-14.10924174513392</v>
       </c>
       <c r="F11">
-        <v>-2.860756204039364</v>
+        <v>-2.560748038502273</v>
       </c>
       <c r="G11">
-        <v>-3.890653584786011</v>
+        <v>-4.71319172947333</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.1768865108686</v>
       </c>
       <c r="E12">
-        <v>-14.87778265439768</v>
+        <v>-14.96373761953727</v>
       </c>
       <c r="F12">
-        <v>-2.766847505053595</v>
+        <v>-2.603152165851579</v>
       </c>
       <c r="G12">
-        <v>-3.870346698448122</v>
+        <v>-3.5082359168171</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.95698165607528</v>
       </c>
       <c r="E13">
-        <v>-15.30341845485262</v>
+        <v>-15.87456318212203</v>
       </c>
       <c r="F13">
-        <v>-2.546500947541524</v>
+        <v>-2.353750621686316</v>
       </c>
       <c r="G13">
-        <v>-2.715850220901463</v>
+        <v>-3.30505449488987</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.787909543339742</v>
       </c>
       <c r="E14">
-        <v>-17.06938293514983</v>
+        <v>-17.01089316486675</v>
       </c>
       <c r="F14">
-        <v>-2.470054233406769</v>
+        <v>-2.262906053723502</v>
       </c>
       <c r="G14">
-        <v>-2.89796664156231</v>
+        <v>-3.32667566780685</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.647571468088187</v>
       </c>
       <c r="E15">
-        <v>-17.04850214150046</v>
+        <v>-17.93490564376185</v>
       </c>
       <c r="F15">
-        <v>-2.336619155429019</v>
+        <v>-2.242611880722317</v>
       </c>
       <c r="G15">
-        <v>-2.569878336438378</v>
+        <v>-2.380756801416433</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.527218332240123</v>
       </c>
       <c r="E16">
-        <v>-18.07394338121935</v>
+        <v>-17.80526448987026</v>
       </c>
       <c r="F16">
-        <v>-2.198659534697178</v>
+        <v>-1.645517201477808</v>
       </c>
       <c r="G16">
-        <v>-2.881311286954237</v>
+        <v>-2.094427717724868</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.412694796450309</v>
       </c>
       <c r="E17">
-        <v>-19.84517900526149</v>
+        <v>-19.71484952332073</v>
       </c>
       <c r="F17">
-        <v>-1.742274655961804</v>
+        <v>-1.655084844980142</v>
       </c>
       <c r="G17">
-        <v>-1.6891010746242</v>
+        <v>-1.832765508846413</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.302966350834552</v>
       </c>
       <c r="E18">
-        <v>-19.41867826627108</v>
+        <v>-19.78319325304449</v>
       </c>
       <c r="F18">
-        <v>-1.522306662352812</v>
+        <v>-1.340486644377543</v>
       </c>
       <c r="G18">
-        <v>-2.251105906461956</v>
+        <v>-1.397250000973131</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.194872171124431</v>
       </c>
       <c r="E19">
-        <v>-20.25104348819894</v>
+        <v>-20.34748187066629</v>
       </c>
       <c r="F19">
-        <v>-1.216817189711397</v>
+        <v>-0.7989613356150337</v>
       </c>
       <c r="G19">
-        <v>-2.760145320216911</v>
+        <v>-1.700317202911251</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.096015368719345</v>
       </c>
       <c r="E20">
-        <v>-20.97674503335014</v>
+        <v>-20.82609176006296</v>
       </c>
       <c r="F20">
-        <v>-1.042155094463718</v>
+        <v>-0.8893842645698221</v>
       </c>
       <c r="G20">
-        <v>-2.479364710849165</v>
+        <v>-1.548422752478411</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.012077875530496</v>
       </c>
       <c r="E21">
-        <v>-22.08235837690084</v>
+        <v>-22.05102133676776</v>
       </c>
       <c r="F21">
-        <v>-0.7163424559620194</v>
+        <v>-0.2402623138576848</v>
       </c>
       <c r="G21">
-        <v>-2.033963913995619</v>
+        <v>-1.948114847071239</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.955505342238111</v>
       </c>
       <c r="E22">
-        <v>-22.40155239580549</v>
+        <v>-22.22553513960135</v>
       </c>
       <c r="F22">
-        <v>-0.1983204155191402</v>
+        <v>0.01513329683423642</v>
       </c>
       <c r="G22">
-        <v>-2.574916986749149</v>
+        <v>-1.995899261385079</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.933356596584375</v>
       </c>
       <c r="E23">
-        <v>-22.86822522771794</v>
+        <v>-22.77250687261781</v>
       </c>
       <c r="F23">
-        <v>0.2095254468817936</v>
+        <v>0.1346807953040527</v>
       </c>
       <c r="G23">
-        <v>-3.482168681240879</v>
+        <v>-2.083622097084687</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.954500040165579</v>
       </c>
       <c r="E24">
-        <v>-23.99269513703657</v>
+        <v>-23.63632234652895</v>
       </c>
       <c r="F24">
-        <v>0.4306929164900392</v>
+        <v>0.2962124388499562</v>
       </c>
       <c r="G24">
-        <v>-3.660524322169114</v>
+        <v>-2.360350598712365</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.018637010105243</v>
       </c>
       <c r="E25">
-        <v>-23.24531125833665</v>
+        <v>-23.60966322004579</v>
       </c>
       <c r="F25">
-        <v>0.5506562553960608</v>
+        <v>0.5960789535611689</v>
       </c>
       <c r="G25">
-        <v>-3.980991751461643</v>
+        <v>-2.242640841518039</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.124123928442837</v>
       </c>
       <c r="E26">
-        <v>-23.4267083416619</v>
+        <v>-23.78896361990549</v>
       </c>
       <c r="F26">
-        <v>0.5768865092057072</v>
+        <v>0.4692948374604962</v>
       </c>
       <c r="G26">
-        <v>-4.041260233004075</v>
+        <v>-2.546492642748967</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.260025611997758</v>
       </c>
       <c r="E27">
-        <v>-24.14075359471736</v>
+        <v>-22.75087435228317</v>
       </c>
       <c r="F27">
-        <v>0.5189123881533809</v>
+        <v>0.7237104895149056</v>
       </c>
       <c r="G27">
-        <v>-4.55584812108285</v>
+        <v>-3.357414083138983</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.414724400861071</v>
       </c>
       <c r="E28">
-        <v>-23.93614808210279</v>
+        <v>-23.16892043030126</v>
       </c>
       <c r="F28">
-        <v>0.8433565637056549</v>
+        <v>0.856742980934895</v>
       </c>
       <c r="G28">
-        <v>-4.453982634839475</v>
+        <v>-3.674653730530723</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.570182913237606</v>
       </c>
       <c r="E29">
-        <v>-24.00242229920505</v>
+        <v>-23.48743064963076</v>
       </c>
       <c r="F29">
-        <v>0.6802046335198755</v>
+        <v>0.8632175005551759</v>
       </c>
       <c r="G29">
-        <v>-5.036906803939885</v>
+        <v>-3.940281972965225</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.710216962293932</v>
       </c>
       <c r="E30">
-        <v>-23.17476216177116</v>
+        <v>-23.02740108908755</v>
       </c>
       <c r="F30">
-        <v>0.6753885054399992</v>
+        <v>0.8883236597992232</v>
       </c>
       <c r="G30">
-        <v>-5.042342719715368</v>
+        <v>-4.050791293611637</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.818604797995924</v>
       </c>
       <c r="E31">
-        <v>-22.98486966120752</v>
+        <v>-21.52632516739502</v>
       </c>
       <c r="F31">
-        <v>0.6462597940879573</v>
+        <v>1.242518650623041</v>
       </c>
       <c r="G31">
-        <v>-5.500538775078197</v>
+        <v>-4.46862848830521</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.883733617839519</v>
       </c>
       <c r="E32">
-        <v>-22.54285889874083</v>
+        <v>-22.0568313689196</v>
       </c>
       <c r="F32">
-        <v>0.7785384711713992</v>
+        <v>0.7483030609692173</v>
       </c>
       <c r="G32">
-        <v>-5.429696411083333</v>
+        <v>-4.403132655356269</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.898312511611413</v>
       </c>
       <c r="E33">
-        <v>-22.15610457611574</v>
+        <v>-22.26275466747039</v>
       </c>
       <c r="F33">
-        <v>0.2055525968179672</v>
+        <v>0.6042392008461468</v>
       </c>
       <c r="G33">
-        <v>-5.578498811982493</v>
+        <v>-4.561327073950343</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.859960682984863</v>
       </c>
       <c r="E34">
-        <v>-21.28317781250118</v>
+        <v>-22.08438713325627</v>
       </c>
       <c r="F34">
-        <v>0.748758663040757</v>
+        <v>0.8861235159773878</v>
       </c>
       <c r="G34">
-        <v>-4.769523972369568</v>
+        <v>-4.369073762848247</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.772354341138238</v>
       </c>
       <c r="E35">
-        <v>-20.85945755655148</v>
+        <v>-21.28304648675496</v>
       </c>
       <c r="F35">
-        <v>0.7118780895333174</v>
+        <v>0.6820237283364232</v>
       </c>
       <c r="G35">
-        <v>-5.282085806578309</v>
+        <v>-4.316876391330559</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.640733334898511</v>
       </c>
       <c r="E36">
-        <v>-20.99174333926354</v>
+        <v>-20.48135261928104</v>
       </c>
       <c r="F36">
-        <v>0.3684021729017248</v>
+        <v>0.4326089302927145</v>
       </c>
       <c r="G36">
-        <v>-5.265744953796466</v>
+        <v>-4.525801609768424</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.475626472683211</v>
       </c>
       <c r="E37">
-        <v>-20.36195940206881</v>
+        <v>-19.75883911983124</v>
       </c>
       <c r="F37">
-        <v>0.4756343331941208</v>
+        <v>0.669043211134555</v>
       </c>
       <c r="G37">
-        <v>-4.398067520681185</v>
+        <v>-4.335597526355137</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.286690061821401</v>
       </c>
       <c r="E38">
-        <v>-20.08611193636558</v>
+        <v>-20.01281858455144</v>
       </c>
       <c r="F38">
-        <v>0.1802931896044019</v>
+        <v>0.4663533048131551</v>
       </c>
       <c r="G38">
-        <v>-4.573056336795981</v>
+        <v>-3.83142792508845</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.088259171753811</v>
       </c>
       <c r="E39">
-        <v>-20.24457682731599</v>
+        <v>-19.25139190795372</v>
       </c>
       <c r="F39">
-        <v>-0.2378037194061758</v>
+        <v>0.2317861640972247</v>
       </c>
       <c r="G39">
-        <v>-4.237138591471672</v>
+        <v>-3.820622304448269</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.890574901135536</v>
       </c>
       <c r="E40">
-        <v>-19.12943104597915</v>
+        <v>-19.13962011249641</v>
       </c>
       <c r="F40">
-        <v>0.01932152242279072</v>
+        <v>0.1215453733978609</v>
       </c>
       <c r="G40">
-        <v>-3.962515596806971</v>
+        <v>-3.909758743093145</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.706785002730747</v>
       </c>
       <c r="E41">
-        <v>-18.30541180164742</v>
+        <v>-18.28425024260958</v>
       </c>
       <c r="F41">
-        <v>-0.03909246172042202</v>
+        <v>0.1678527679491589</v>
       </c>
       <c r="G41">
-        <v>-3.860143597096088</v>
+        <v>-3.076848659231289</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.543684072876189</v>
       </c>
       <c r="E42">
-        <v>-18.22644427190166</v>
+        <v>-18.55662436874892</v>
       </c>
       <c r="F42">
-        <v>-0.2935279945924986</v>
+        <v>-0.1732755554628999</v>
       </c>
       <c r="G42">
-        <v>-3.011998382662506</v>
+        <v>-3.551491504833217</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.409272701031651</v>
       </c>
       <c r="E43">
-        <v>-17.88845255739117</v>
+        <v>-18.22707825826274</v>
       </c>
       <c r="F43">
-        <v>-0.2312181985539198</v>
+        <v>0.04372274100705575</v>
       </c>
       <c r="G43">
-        <v>-3.492583657507426</v>
+        <v>-3.009247319319372</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.304512169140509</v>
       </c>
       <c r="E44">
-        <v>-17.90489997498703</v>
+        <v>-17.02805608135582</v>
       </c>
       <c r="F44">
-        <v>-0.4471064827041241</v>
+        <v>-0.03821687737566294</v>
       </c>
       <c r="G44">
-        <v>-3.609571715774191</v>
+        <v>-2.715439713254593</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.230725709653928</v>
       </c>
       <c r="E45">
-        <v>-17.39530626642988</v>
+        <v>-16.09197521923029</v>
       </c>
       <c r="F45">
-        <v>-0.6698619326235363</v>
+        <v>-0.200341631981971</v>
       </c>
       <c r="G45">
-        <v>-2.575380463124647</v>
+        <v>-2.762999010471763</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.183135917668383</v>
       </c>
       <c r="E46">
-        <v>-16.57128702209815</v>
+        <v>-15.49555255005006</v>
       </c>
       <c r="F46">
-        <v>-0.7573540977072202</v>
+        <v>-0.4268984599128302</v>
       </c>
       <c r="G46">
-        <v>-2.877815350864766</v>
+        <v>-2.382345863275283</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.157290128863357</v>
       </c>
       <c r="E47">
-        <v>-15.18150287761812</v>
+        <v>-15.4426780875365</v>
       </c>
       <c r="F47">
-        <v>-1.178371830180069</v>
+        <v>-0.6499430100558194</v>
       </c>
       <c r="G47">
-        <v>-3.336455019329857</v>
+        <v>-2.971854707453303</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.145128693841966</v>
       </c>
       <c r="E48">
-        <v>-14.28282268232193</v>
+        <v>-14.77402172945993</v>
       </c>
       <c r="F48">
-        <v>-1.348887118209333</v>
+        <v>-0.6178139519708379</v>
       </c>
       <c r="G48">
-        <v>-2.735336091945613</v>
+        <v>-2.549144389725923</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.140629328652166</v>
       </c>
       <c r="E49">
-        <v>-14.75171446649814</v>
+        <v>-14.19795002247017</v>
       </c>
       <c r="F49">
-        <v>-1.326621430789485</v>
+        <v>-0.6250505696016944</v>
       </c>
       <c r="G49">
-        <v>-2.87947724472548</v>
+        <v>-2.438433125801616</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.138321135985686</v>
       </c>
       <c r="E50">
-        <v>-14.37975466845612</v>
+        <v>-14.50008980826194</v>
       </c>
       <c r="F50">
-        <v>-0.9641245418548103</v>
+        <v>-0.6655651909052154</v>
       </c>
       <c r="G50">
-        <v>-2.559165411073297</v>
+        <v>-2.556483869186487</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.137211327067833</v>
       </c>
       <c r="E51">
-        <v>-14.63749729507668</v>
+        <v>-13.54964915505808</v>
       </c>
       <c r="F51">
-        <v>-1.302809181428611</v>
+        <v>-0.7371767245098297</v>
       </c>
       <c r="G51">
-        <v>-3.300999076604263</v>
+        <v>-2.778154687950547</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.137830304330052</v>
       </c>
       <c r="E52">
-        <v>-13.45484102323349</v>
+        <v>-12.87677225920635</v>
       </c>
       <c r="F52">
-        <v>-1.284389603859961</v>
+        <v>-1.214305579746109</v>
       </c>
       <c r="G52">
-        <v>-2.666900494557799</v>
+        <v>-2.517439295096322</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.144598821079026</v>
       </c>
       <c r="E53">
-        <v>-13.36474250437688</v>
+        <v>-12.7982802192314</v>
       </c>
       <c r="F53">
-        <v>-1.307920208303884</v>
+        <v>-0.9424710179456313</v>
       </c>
       <c r="G53">
-        <v>-3.129847182769482</v>
+        <v>-2.293047207898983</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.162345177708743</v>
       </c>
       <c r="E54">
-        <v>-12.90345402805955</v>
+        <v>-12.07199902940723</v>
       </c>
       <c r="F54">
-        <v>-1.525454458483451</v>
+        <v>-1.00962179308617</v>
       </c>
       <c r="G54">
-        <v>-3.069701191412003</v>
+        <v>-2.689074528579837</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.198800227700542</v>
       </c>
       <c r="E55">
-        <v>-12.22835817994407</v>
+        <v>-11.33788810802378</v>
       </c>
       <c r="F55">
-        <v>-1.847342292230685</v>
+        <v>-0.8749449923716239</v>
       </c>
       <c r="G55">
-        <v>-3.159205100611739</v>
+        <v>-2.417232392168123</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.260579099525377</v>
       </c>
       <c r="E56">
-        <v>-12.1666214937975</v>
+        <v>-11.00742724578805</v>
       </c>
       <c r="F56">
-        <v>-1.501281040934955</v>
+        <v>-1.138514104226968</v>
       </c>
       <c r="G56">
-        <v>-3.721130479356551</v>
+        <v>-3.036516282926348</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.354449453182125</v>
       </c>
       <c r="E57">
-        <v>-11.85878488770408</v>
+        <v>-10.93730382577927</v>
       </c>
       <c r="F57">
-        <v>-1.489238235633056</v>
+        <v>-1.300401945756075</v>
       </c>
       <c r="G57">
-        <v>-3.661772397837419</v>
+        <v>-3.651797724127595</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.48468661832485</v>
       </c>
       <c r="E58">
-        <v>-11.01428788390967</v>
+        <v>-10.45269370832244</v>
       </c>
       <c r="F58">
-        <v>-1.477925222013023</v>
+        <v>-1.328683237255053</v>
       </c>
       <c r="G58">
-        <v>-4.563101526359392</v>
+        <v>-3.414626931148668</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.652011411715879</v>
       </c>
       <c r="E59">
-        <v>-10.82493427175294</v>
+        <v>-10.15400914819852</v>
       </c>
       <c r="F59">
-        <v>-1.833747954783343</v>
+        <v>-1.4328827444858</v>
       </c>
       <c r="G59">
-        <v>-3.865460333232158</v>
+        <v>-3.169179774321563</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.854071183354088</v>
       </c>
       <c r="E60">
-        <v>-10.49209596066318</v>
+        <v>-9.722889365720288</v>
       </c>
       <c r="F60">
-        <v>-1.662380276696598</v>
+        <v>-1.466253525307578</v>
       </c>
       <c r="G60">
-        <v>-4.658789534626487</v>
+        <v>-3.910761838391544</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.082590848053326</v>
       </c>
       <c r="E61">
-        <v>-11.55555826815048</v>
+        <v>-10.08490010636747</v>
       </c>
       <c r="F61">
-        <v>-2.058559412596503</v>
+        <v>-1.423115464439391</v>
       </c>
       <c r="G61">
-        <v>-4.279579785285129</v>
+        <v>-3.670790323886394</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.328837843553704</v>
       </c>
       <c r="E62">
-        <v>-10.33573681012633</v>
+        <v>-9.773245996685583</v>
       </c>
       <c r="F62">
-        <v>-2.067972979761917</v>
+        <v>-1.393212229565732</v>
       </c>
       <c r="G62">
-        <v>-4.888117645222881</v>
+        <v>-4.238108581314679</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.579529649739391</v>
       </c>
       <c r="E63">
-        <v>-9.163903591161475</v>
+        <v>-9.20695126507839</v>
       </c>
       <c r="F63">
-        <v>-1.936677574785598</v>
+        <v>-1.318548990449204</v>
       </c>
       <c r="G63">
-        <v>-4.714310693865604</v>
+        <v>-4.183044277359982</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.826265726709146</v>
       </c>
       <c r="E64">
-        <v>-9.956925430910701</v>
+        <v>-8.91354690564742</v>
       </c>
       <c r="F64">
-        <v>-1.856726866537001</v>
+        <v>-1.456167323811091</v>
       </c>
       <c r="G64">
-        <v>-5.558976524937411</v>
+        <v>-4.570143056721422</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.057992377257126</v>
       </c>
       <c r="E65">
-        <v>-9.172806571060555</v>
+        <v>-9.374359892193947</v>
       </c>
       <c r="F65">
-        <v>-2.234520387931771</v>
+        <v>-1.776101867222525</v>
       </c>
       <c r="G65">
-        <v>-5.32791368847844</v>
+        <v>-4.160823895700394</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.271072094317768</v>
       </c>
       <c r="E66">
-        <v>-9.109806440665846</v>
+        <v>-8.98410958763494</v>
       </c>
       <c r="F66">
-        <v>-2.208837684975375</v>
+        <v>-1.749247024391168</v>
       </c>
       <c r="G66">
-        <v>-5.509295168029569</v>
+        <v>-4.009184357274076</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.459085162372934</v>
       </c>
       <c r="E67">
-        <v>-9.614486754924675</v>
+        <v>-8.770338443628852</v>
       </c>
       <c r="F67">
-        <v>-2.063021827795384</v>
+        <v>-1.61994632812079</v>
       </c>
       <c r="G67">
-        <v>-5.400163034327494</v>
+        <v>-4.653919722138219</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.625016560745885</v>
       </c>
       <c r="E68">
-        <v>-8.86273289880735</v>
+        <v>-9.086493856474359</v>
       </c>
       <c r="F68">
-        <v>-2.40035871360483</v>
+        <v>-1.974197647927999</v>
       </c>
       <c r="G68">
-        <v>-5.595885797154746</v>
+        <v>-4.111324618797211</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.768356586946304</v>
       </c>
       <c r="E69">
-        <v>-8.778476111420636</v>
+        <v>-8.643799294432519</v>
       </c>
       <c r="F69">
-        <v>-2.167106191957142</v>
+        <v>-1.777196968929026</v>
       </c>
       <c r="G69">
-        <v>-5.290067531873492</v>
+        <v>-4.603467008119726</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.897800347049354</v>
       </c>
       <c r="E70">
-        <v>-8.762934388626311</v>
+        <v>-9.075838357134311</v>
       </c>
       <c r="F70">
-        <v>-2.643853998188133</v>
+        <v>-2.072141324532804</v>
       </c>
       <c r="G70">
-        <v>-5.193214211576573</v>
+        <v>-4.53776592134735</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.016943134270774</v>
       </c>
       <c r="E71">
-        <v>-9.094287360241559</v>
+        <v>-9.297235451369314</v>
       </c>
       <c r="F71">
-        <v>-2.243140379125303</v>
+        <v>-2.097632674619153</v>
       </c>
       <c r="G71">
-        <v>-5.14785642714302</v>
+        <v>-4.356500310890095</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.136286981280974</v>
       </c>
       <c r="E72">
-        <v>-9.177937332111245</v>
+        <v>-9.007915775493263</v>
       </c>
       <c r="F72">
-        <v>-2.450861789051307</v>
+        <v>-1.80855150349239</v>
       </c>
       <c r="G72">
-        <v>-4.915860016841973</v>
+        <v>-4.163409431766564</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.25901690808125</v>
       </c>
       <c r="E73">
-        <v>-9.328056245465518</v>
+        <v>-9.200126854748831</v>
       </c>
       <c r="F73">
-        <v>-2.321958709134273</v>
+        <v>-2.193031606562558</v>
       </c>
       <c r="G73">
-        <v>-5.528903529258672</v>
+        <v>-4.818430661621222</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.389863922014955</v>
       </c>
       <c r="E74">
-        <v>-9.593741815495537</v>
+        <v>-10.0977881433933</v>
       </c>
       <c r="F74">
-        <v>-2.449259726494293</v>
+        <v>-2.139128911294991</v>
       </c>
       <c r="G74">
-        <v>-5.407999095618949</v>
+        <v>-4.674547731393417</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.526279651818838</v>
       </c>
       <c r="E75">
-        <v>-10.99840199709076</v>
+        <v>-9.049464524513638</v>
       </c>
       <c r="F75">
-        <v>-2.323543375975829</v>
+        <v>-2.380303110415651</v>
       </c>
       <c r="G75">
-        <v>-5.400507331063578</v>
+        <v>-4.371867863283392</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.663194844954115</v>
       </c>
       <c r="E76">
-        <v>-10.93895219031806</v>
+        <v>-10.2071870184706</v>
       </c>
       <c r="F76">
-        <v>-2.492932912704688</v>
+        <v>-2.408837053972483</v>
       </c>
       <c r="G76">
-        <v>-4.656856176031552</v>
+        <v>-4.575141980485721</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.791706423289349</v>
       </c>
       <c r="E77">
-        <v>-11.08795257059244</v>
+        <v>-10.11169961554486</v>
       </c>
       <c r="F77">
-        <v>-2.425364640393138</v>
+        <v>-2.246908622440638</v>
       </c>
       <c r="G77">
-        <v>-4.776297348542918</v>
+        <v>-4.05786592942906</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.899135313765267</v>
       </c>
       <c r="E78">
-        <v>-11.6453126229825</v>
+        <v>-10.92177115993296</v>
       </c>
       <c r="F78">
-        <v>-2.916671832095733</v>
+        <v>-2.380270804086941</v>
       </c>
       <c r="G78">
-        <v>-4.34180479924127</v>
+        <v>-3.930049076703338</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.975349852489888</v>
       </c>
       <c r="E79">
-        <v>-10.94114850021178</v>
+        <v>-11.52017277225454</v>
       </c>
       <c r="F79">
-        <v>-2.80849367622934</v>
+        <v>-2.550826682118943</v>
       </c>
       <c r="G79">
-        <v>-4.203056525144876</v>
+        <v>-3.665619251754052</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.008193723161972</v>
       </c>
       <c r="E80">
-        <v>-12.25873065511351</v>
+        <v>-11.6786104923609</v>
       </c>
       <c r="F80">
-        <v>-2.936695957323606</v>
+        <v>-2.33544784392146</v>
       </c>
       <c r="G80">
-        <v>-4.542013351274235</v>
+        <v>-4.019211999712529</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.994221080816463</v>
       </c>
       <c r="E81">
-        <v>-12.97291629086321</v>
+        <v>-12.25271231315732</v>
       </c>
       <c r="F81">
-        <v>-2.801120377977022</v>
+        <v>-2.718281980962266</v>
       </c>
       <c r="G81">
-        <v>-4.091368650286483</v>
+        <v>-3.157112835830919</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.929935932341438</v>
       </c>
       <c r="E82">
-        <v>-13.54112203850164</v>
+        <v>-13.59593921636448</v>
       </c>
       <c r="F82">
-        <v>-3.226459703190276</v>
+        <v>-2.619129716316776</v>
       </c>
       <c r="G82">
-        <v>-4.136577460170771</v>
+        <v>-3.914886778133476</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.82104860039045</v>
       </c>
       <c r="E83">
-        <v>-15.06714532350242</v>
+        <v>-14.16486499137013</v>
       </c>
       <c r="F83">
-        <v>-3.402301393619541</v>
+        <v>-2.624377423813511</v>
       </c>
       <c r="G83">
-        <v>-3.799593719182818</v>
+        <v>-3.832894496762347</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.670864930103089</v>
       </c>
       <c r="E84">
-        <v>-16.33022276524783</v>
+        <v>-15.22069682015451</v>
       </c>
       <c r="F84">
-        <v>-3.302015922367021</v>
+        <v>-2.871521666806146</v>
       </c>
       <c r="G84">
-        <v>-4.088167352750008</v>
+        <v>-3.38109441538139</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.490308859210153</v>
       </c>
       <c r="E85">
-        <v>-16.15982987376122</v>
+        <v>-15.17897146064784</v>
       </c>
       <c r="F85">
-        <v>-2.968524318041371</v>
+        <v>-2.794945727356554</v>
       </c>
       <c r="G85">
-        <v>-3.994240554709807</v>
+        <v>-3.52567587071798</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.28685531062428</v>
       </c>
       <c r="E86">
-        <v>-17.90656192494784</v>
+        <v>-17.91643399828457</v>
       </c>
       <c r="F86">
-        <v>-3.355086936762177</v>
+        <v>-2.871732072126457</v>
       </c>
       <c r="G86">
-        <v>-3.252655180094286</v>
+        <v>-3.123057253868437</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.072831864435114</v>
       </c>
       <c r="E87">
-        <v>-19.02080653995716</v>
+        <v>-17.63378929309582</v>
       </c>
       <c r="F87">
-        <v>-3.728799091963355</v>
+        <v>-3.133876392048986</v>
       </c>
       <c r="G87">
-        <v>-3.931714281109592</v>
+        <v>-3.246010915196968</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.856438387334666</v>
       </c>
       <c r="E88">
-        <v>-20.4049300919276</v>
+        <v>-19.94941541997004</v>
       </c>
       <c r="F88">
-        <v>-3.716534284197505</v>
+        <v>-3.048726849980419</v>
       </c>
       <c r="G88">
-        <v>-3.437741160103859</v>
+        <v>-3.50560072256784</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.646371656403208</v>
       </c>
       <c r="E89">
-        <v>-21.56142084095447</v>
+        <v>-21.01469364553442</v>
       </c>
       <c r="F89">
-        <v>-3.581541875502492</v>
+        <v>-3.43805455909177</v>
       </c>
       <c r="G89">
-        <v>-3.059435189694723</v>
+        <v>-2.608999053075946</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.447076407387854</v>
       </c>
       <c r="E90">
-        <v>-22.4703987861441</v>
+        <v>-22.63630848836312</v>
       </c>
       <c r="F90">
-        <v>-4.164995828725101</v>
+        <v>-3.192900054600659</v>
       </c>
       <c r="G90">
-        <v>-3.683943121313918</v>
+        <v>-3.043435323103425</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.261335393305203</v>
       </c>
       <c r="E91">
-        <v>-24.18202157834926</v>
+        <v>-24.558537021243</v>
       </c>
       <c r="F91">
-        <v>-3.830577281275719</v>
+        <v>-3.420278622995096</v>
       </c>
       <c r="G91">
-        <v>-4.144724712742917</v>
+        <v>-3.415007643885684</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.091592805222954</v>
       </c>
       <c r="E92">
-        <v>-25.70886904561944</v>
+        <v>-26.0170860435295</v>
       </c>
       <c r="F92">
-        <v>-3.97441665383263</v>
+        <v>-3.368881739120998</v>
       </c>
       <c r="G92">
-        <v>-4.210644295520885</v>
+        <v>-3.765627521949896</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.937860682633115</v>
       </c>
       <c r="E93">
-        <v>-27.93480421629774</v>
+        <v>-27.61931901760537</v>
       </c>
       <c r="F93">
-        <v>-4.304072088715916</v>
+        <v>-3.89829383135237</v>
       </c>
       <c r="G93">
-        <v>-4.419125900856488</v>
+        <v>-3.748336542598282</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.803007779211389</v>
       </c>
       <c r="E94">
-        <v>-30.18032503705922</v>
+        <v>-29.12896281212042</v>
       </c>
       <c r="F94">
-        <v>-4.221497940902653</v>
+        <v>-3.590308487726319</v>
       </c>
       <c r="G94">
-        <v>-5.580653977128559</v>
+        <v>-3.724033827794492</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.685650493238336</v>
       </c>
       <c r="E95">
-        <v>-31.95740239257125</v>
+        <v>-32.05084518948252</v>
       </c>
       <c r="F95">
-        <v>-4.154401009643296</v>
+        <v>-3.878471827770781</v>
       </c>
       <c r="G95">
-        <v>-5.423730808021566</v>
+        <v>-4.819970065296983</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.591367606006995</v>
       </c>
       <c r="E96">
-        <v>-34.42405765607528</v>
+        <v>-34.03607158852011</v>
       </c>
       <c r="F96">
-        <v>-4.308483145135823</v>
+        <v>-3.44680129049793</v>
       </c>
       <c r="G96">
-        <v>-5.521494528341783</v>
+        <v>-4.259935008055094</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.516717514951719</v>
       </c>
       <c r="E97">
-        <v>-36.97174996194658</v>
+        <v>-36.40622054244668</v>
       </c>
       <c r="F97">
-        <v>-4.519841087960118</v>
+        <v>-3.656361676058149</v>
       </c>
       <c r="G97">
-        <v>-5.410306545859821</v>
+        <v>-5.298367069540444</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.473028678125385</v>
       </c>
       <c r="E98">
-        <v>-38.92237429109156</v>
+        <v>-38.80210707839585</v>
       </c>
       <c r="F98">
-        <v>-4.205567607379415</v>
+        <v>-3.767384445585756</v>
       </c>
       <c r="G98">
-        <v>-5.677808557069551</v>
+        <v>-5.032142928908874</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.454159987445475</v>
       </c>
       <c r="E99">
-        <v>-41.76732921624836</v>
+        <v>-41.49631136807431</v>
       </c>
       <c r="F99">
-        <v>-4.441868521069406</v>
+        <v>-3.987369006542804</v>
       </c>
       <c r="G99">
-        <v>-7.096506431923286</v>
+        <v>-5.260080610378774</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.482592055639912</v>
       </c>
       <c r="E100">
-        <v>-43.9591061074868</v>
+        <v>-43.84547763768634</v>
       </c>
       <c r="F100">
-        <v>-4.455210206458895</v>
+        <v>-3.914524033875421</v>
       </c>
       <c r="G100">
-        <v>-6.938530509334805</v>
+        <v>-5.646408032629564</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.541257836572927</v>
       </c>
       <c r="E101">
-        <v>-45.82728503884814</v>
+        <v>-45.92351058303713</v>
       </c>
       <c r="F101">
-        <v>-4.693775876628138</v>
+        <v>-4.126938973505687</v>
       </c>
       <c r="G101">
-        <v>-7.241511637088903</v>
+        <v>-7.155834718532565</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.675744762667238</v>
       </c>
       <c r="E102">
-        <v>-48.58264070940768</v>
+        <v>-48.76793341249802</v>
       </c>
       <c r="F102">
-        <v>-4.507807394699649</v>
+        <v>-4.23392179520984</v>
       </c>
       <c r="G102">
-        <v>-7.278344766758835</v>
+        <v>-6.328539319905313</v>
       </c>
     </row>
   </sheetData>
